--- a/Results/tables/Ecological_Covariate_Effects_Synthesis.xlsx
+++ b/Results/tables/Ecological_Covariate_Effects_Synthesis.xlsx
@@ -424,16 +424,16 @@
         </is>
       </c>
       <c r="E2">
-        <v>-1.464</v>
+        <v>-1.407</v>
       </c>
       <c r="F2">
-        <v>0.594</v>
+        <v>0.598</v>
       </c>
       <c r="G2">
-        <v>-2.727</v>
+        <v>-2.666</v>
       </c>
       <c r="H2">
-        <v>-0.42</v>
+        <v>-0.31</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="E3">
-        <v>1.264</v>
+        <v>1.225</v>
       </c>
       <c r="F3">
-        <v>0.415</v>
+        <v>0.438</v>
       </c>
       <c r="G3">
-        <v>0.457</v>
+        <v>0.413</v>
       </c>
       <c r="H3">
-        <v>2.067</v>
+        <v>2.14</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -504,16 +504,16 @@
         </is>
       </c>
       <c r="E4">
-        <v>-0.257</v>
+        <v>-0.251</v>
       </c>
       <c r="F4">
-        <v>0.398</v>
+        <v>0.432</v>
       </c>
       <c r="G4">
-        <v>-1.133</v>
+        <v>-1.215</v>
       </c>
       <c r="H4">
-        <v>0.432</v>
+        <v>0.511</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         </is>
       </c>
       <c r="E5">
-        <v>-1.014</v>
+        <v>-0.979</v>
       </c>
       <c r="F5">
-        <v>0.835</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="G5">
-        <v>-3.031</v>
+        <v>-2.899</v>
       </c>
       <c r="H5">
-        <v>0.194</v>
+        <v>0.222</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="E6">
-        <v>-1.232</v>
+        <v>-1.189</v>
       </c>
       <c r="F6">
-        <v>0.7</v>
+        <v>0.639</v>
       </c>
       <c r="G6">
-        <v>-2.713</v>
+        <v>-2.529</v>
       </c>
       <c r="H6">
-        <v>-0.027</v>
+        <v>-0.018</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="E7">
-        <v>1.451</v>
+        <v>1.319</v>
       </c>
       <c r="F7">
-        <v>0.474</v>
+        <v>0.477</v>
       </c>
       <c r="G7">
-        <v>0.523</v>
+        <v>0.387</v>
       </c>
       <c r="H7">
-        <v>2.341</v>
+        <v>2.265</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -664,16 +664,16 @@
         </is>
       </c>
       <c r="E8">
-        <v>-0.23</v>
+        <v>-0.239</v>
       </c>
       <c r="F8">
-        <v>0.644</v>
+        <v>0.638</v>
       </c>
       <c r="G8">
-        <v>-1.548</v>
+        <v>-1.498</v>
       </c>
       <c r="H8">
-        <v>1</v>
+        <v>1.024</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="E9">
-        <v>-1.039</v>
+        <v>-1.032</v>
       </c>
       <c r="F9">
-        <v>0.847</v>
+        <v>0.793</v>
       </c>
       <c r="G9">
-        <v>-3.019</v>
+        <v>-2.904</v>
       </c>
       <c r="H9">
-        <v>0.17</v>
+        <v>0.155</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -744,16 +744,16 @@
         </is>
       </c>
       <c r="E10">
-        <v>0.119</v>
+        <v>0.095</v>
       </c>
       <c r="F10">
-        <v>0.677</v>
+        <v>0.632</v>
       </c>
       <c r="G10">
-        <v>-1.33</v>
+        <v>-1.271</v>
       </c>
       <c r="H10">
-        <v>1.297</v>
+        <v>1.199</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="E11">
-        <v>-1.337</v>
+        <v>-1.386</v>
       </c>
       <c r="F11">
-        <v>0.7</v>
+        <v>0.651</v>
       </c>
       <c r="G11">
-        <v>-2.882</v>
+        <v>-2.7</v>
       </c>
       <c r="H11">
-        <v>-0.123</v>
+        <v>-0.165</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -824,16 +824,16 @@
         </is>
       </c>
       <c r="E12">
-        <v>1.226</v>
+        <v>1.211</v>
       </c>
       <c r="F12">
-        <v>0.467</v>
+        <v>0.459</v>
       </c>
       <c r="G12">
-        <v>0.285</v>
+        <v>0.332</v>
       </c>
       <c r="H12">
-        <v>2.145</v>
+        <v>2.124</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         </is>
       </c>
       <c r="E13">
-        <v>-0.077</v>
+        <v>-0.089</v>
       </c>
       <c r="F13">
-        <v>0.521</v>
+        <v>0.534</v>
       </c>
       <c r="G13">
-        <v>-1.081</v>
+        <v>-1.138</v>
       </c>
       <c r="H13">
-        <v>1.005</v>
+        <v>0.946</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E14">
-        <v>-0.267</v>
+        <v>-0.252</v>
       </c>
       <c r="F14">
-        <v>0.471</v>
+        <v>0.443</v>
       </c>
       <c r="G14">
-        <v>-1.308</v>
+        <v>-1.227</v>
       </c>
       <c r="H14">
-        <v>0.545</v>
+        <v>0.512</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -944,16 +944,16 @@
         </is>
       </c>
       <c r="E15">
-        <v>-0.968</v>
+        <v>-0.994</v>
       </c>
       <c r="F15">
-        <v>0.796</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="G15">
-        <v>-2.841</v>
+        <v>-2.869</v>
       </c>
       <c r="H15">
-        <v>0.24</v>
+        <v>0.225</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -984,16 +984,16 @@
         </is>
       </c>
       <c r="E16">
-        <v>-1.362</v>
+        <v>-1.278</v>
       </c>
       <c r="F16">
-        <v>0.609</v>
+        <v>0.636</v>
       </c>
       <c r="G16">
-        <v>-2.699</v>
+        <v>-2.589</v>
       </c>
       <c r="H16">
-        <v>-0.253</v>
+        <v>-0.077</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="E17">
-        <v>1.038</v>
+        <v>1.248</v>
       </c>
       <c r="F17">
-        <v>0.43</v>
+        <v>0.478</v>
       </c>
       <c r="G17">
-        <v>0.254</v>
+        <v>0.316</v>
       </c>
       <c r="H17">
-        <v>1.923</v>
+        <v>2.195</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="E18">
-        <v>-0.094</v>
+        <v>-0.13</v>
       </c>
       <c r="F18">
-        <v>0.477</v>
+        <v>0.517</v>
       </c>
       <c r="G18">
-        <v>-1.046</v>
+        <v>-1.158</v>
       </c>
       <c r="H18">
-        <v>0.8159999999999999</v>
+        <v>0.865</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1104,16 +1104,16 @@
         </is>
       </c>
       <c r="E19">
-        <v>-1.107</v>
+        <v>-1.056</v>
       </c>
       <c r="F19">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="G19">
-        <v>-2.963</v>
+        <v>-2.932</v>
       </c>
       <c r="H19">
-        <v>0.06900000000000001</v>
+        <v>0.132</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1144,16 +1144,16 @@
         </is>
       </c>
       <c r="E20">
-        <v>-0.151</v>
+        <v>-0.251</v>
       </c>
       <c r="F20">
-        <v>0.428</v>
+        <v>0.426</v>
       </c>
       <c r="G20">
-        <v>-1.216</v>
+        <v>-1.287</v>
       </c>
       <c r="H20">
-        <v>0.47</v>
+        <v>0.372</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         </is>
       </c>
       <c r="E21">
-        <v>1.007</v>
+        <v>1.07</v>
       </c>
       <c r="F21">
-        <v>0.377</v>
+        <v>0.503</v>
       </c>
       <c r="G21">
-        <v>0.309</v>
+        <v>0.101</v>
       </c>
       <c r="H21">
-        <v>1.761</v>
+        <v>2.06</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="E22">
-        <v>-0.706</v>
+        <v>-0.39</v>
       </c>
       <c r="F22">
-        <v>0.428</v>
+        <v>0.525</v>
       </c>
       <c r="G22">
-        <v>-1.57</v>
+        <v>-1.415</v>
       </c>
       <c r="H22">
-        <v>0.112</v>
+        <v>0.645</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1264,16 +1264,16 @@
         </is>
       </c>
       <c r="E23">
-        <v>0.97</v>
+        <v>1.051</v>
       </c>
       <c r="F23">
-        <v>0.336</v>
+        <v>0.406</v>
       </c>
       <c r="G23">
-        <v>0.292</v>
+        <v>0.227</v>
       </c>
       <c r="H23">
-        <v>1.587</v>
+        <v>1.853</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1304,16 +1304,16 @@
         </is>
       </c>
       <c r="E24">
-        <v>1.126</v>
+        <v>1.033</v>
       </c>
       <c r="F24">
-        <v>0.475</v>
+        <v>0.476</v>
       </c>
       <c r="G24">
-        <v>0.212</v>
+        <v>0.14</v>
       </c>
       <c r="H24">
-        <v>2.099</v>
+        <v>2.006</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         </is>
       </c>
       <c r="E25">
-        <v>-0.633</v>
+        <v>-0.443</v>
       </c>
       <c r="F25">
-        <v>0.497</v>
+        <v>0.515</v>
       </c>
       <c r="G25">
-        <v>-1.649</v>
+        <v>-1.451</v>
       </c>
       <c r="H25">
-        <v>0.3</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1384,16 +1384,16 @@
         </is>
       </c>
       <c r="E26">
-        <v>-1.221</v>
+        <v>-1.266</v>
       </c>
       <c r="F26">
-        <v>0.824</v>
+        <v>0.866</v>
       </c>
       <c r="G26">
-        <v>-3.09</v>
+        <v>-3.246</v>
       </c>
       <c r="H26">
-        <v>0.043</v>
+        <v>0.036</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="E27">
-        <v>1.093</v>
+        <v>1.039</v>
       </c>
       <c r="F27">
-        <v>0.385</v>
+        <v>0.399</v>
       </c>
       <c r="G27">
-        <v>0.328</v>
+        <v>0.237</v>
       </c>
       <c r="H27">
-        <v>1.869</v>
+        <v>1.819</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1464,20 +1464,20 @@
         </is>
       </c>
       <c r="E28">
-        <v>-0.537</v>
+        <v>-0.181</v>
       </c>
       <c r="F28">
-        <v>0.204</v>
+        <v>0.105</v>
       </c>
       <c r="G28">
-        <v>-0.927</v>
+        <v>-0.386</v>
       </c>
       <c r="H28">
-        <v>-0.112</v>
+        <v>0.023</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Negative (-)</t>
+          <t>Overlap 0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1504,16 +1504,16 @@
         </is>
       </c>
       <c r="E29">
-        <v>-0.291</v>
+        <v>-0.432</v>
       </c>
       <c r="F29">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
       <c r="G29">
-        <v>-0.553</v>
+        <v>-0.661</v>
       </c>
       <c r="H29">
-        <v>-0.051</v>
+        <v>-0.204</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="E30">
-        <v>-0.291</v>
+        <v>-0.495</v>
       </c>
       <c r="F30">
-        <v>0.127</v>
+        <v>0.111</v>
       </c>
       <c r="G30">
-        <v>-0.553</v>
+        <v>-0.716</v>
       </c>
       <c r="H30">
-        <v>-0.051</v>
+        <v>-0.28</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1584,20 +1584,20 @@
         </is>
       </c>
       <c r="E31">
-        <v>0.323</v>
+        <v>0.188</v>
       </c>
       <c r="F31">
-        <v>0.142</v>
+        <v>0.116</v>
       </c>
       <c r="G31">
-        <v>0.024</v>
+        <v>-0.047</v>
       </c>
       <c r="H31">
-        <v>0.587</v>
+        <v>0.413</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Overlap 0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -1624,16 +1624,16 @@
         </is>
       </c>
       <c r="E32">
-        <v>-0.537</v>
+        <v>-0.294</v>
       </c>
       <c r="F32">
-        <v>0.204</v>
+        <v>0.126</v>
       </c>
       <c r="G32">
-        <v>-0.927</v>
+        <v>-0.539</v>
       </c>
       <c r="H32">
-        <v>-0.112</v>
+        <v>-0.049</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         </is>
       </c>
       <c r="E33">
-        <v>-0.291</v>
+        <v>-0.413</v>
       </c>
       <c r="F33">
-        <v>0.127</v>
+        <v>0.115</v>
       </c>
       <c r="G33">
-        <v>-0.553</v>
+        <v>-0.644</v>
       </c>
       <c r="H33">
-        <v>-0.051</v>
+        <v>-0.195</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1704,16 +1704,16 @@
         </is>
       </c>
       <c r="E34">
-        <v>0.323</v>
+        <v>0.308</v>
       </c>
       <c r="F34">
-        <v>0.142</v>
+        <v>0.135</v>
       </c>
       <c r="G34">
-        <v>0.024</v>
+        <v>0.042</v>
       </c>
       <c r="H34">
-        <v>0.587</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1744,16 +1744,16 @@
         </is>
       </c>
       <c r="E35">
-        <v>-0.537</v>
+        <v>-0.454</v>
       </c>
       <c r="F35">
-        <v>0.204</v>
+        <v>0.158</v>
       </c>
       <c r="G35">
-        <v>-0.927</v>
+        <v>-0.753</v>
       </c>
       <c r="H35">
-        <v>-0.112</v>
+        <v>-0.136</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="E36">
-        <v>-0.291</v>
+        <v>-0.357</v>
       </c>
       <c r="F36">
-        <v>0.127</v>
+        <v>0.121</v>
       </c>
       <c r="G36">
-        <v>-0.553</v>
+        <v>-0.605</v>
       </c>
       <c r="H36">
-        <v>-0.051</v>
+        <v>-0.126</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         </is>
       </c>
       <c r="E37">
-        <v>-1.676</v>
+        <v>-1.584</v>
       </c>
       <c r="F37">
-        <v>1.035</v>
+        <v>1.063</v>
       </c>
       <c r="G37">
-        <v>-3.805</v>
+        <v>-3.784</v>
       </c>
       <c r="H37">
-        <v>0.177</v>
+        <v>0.193</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1864,16 +1864,16 @@
         </is>
       </c>
       <c r="E38">
-        <v>-0.291</v>
+        <v>-0.432</v>
       </c>
       <c r="F38">
-        <v>0.127</v>
+        <v>0.116</v>
       </c>
       <c r="G38">
-        <v>-0.553</v>
+        <v>-0.669</v>
       </c>
       <c r="H38">
-        <v>-0.051</v>
+        <v>-0.218</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1904,16 +1904,16 @@
         </is>
       </c>
       <c r="E39">
-        <v>-0.107</v>
+        <v>-0.186</v>
       </c>
       <c r="F39">
-        <v>0.127</v>
+        <v>0.117</v>
       </c>
       <c r="G39">
-        <v>-0.368</v>
+        <v>-0.427</v>
       </c>
       <c r="H39">
-        <v>0.125</v>
+        <v>0.028</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="E40">
-        <v>-0.129</v>
+        <v>0.096</v>
       </c>
       <c r="F40">
-        <v>0.121</v>
+        <v>0.083</v>
       </c>
       <c r="G40">
-        <v>-0.365</v>
+        <v>-0.066</v>
       </c>
       <c r="H40">
-        <v>0.107</v>
+        <v>0.261</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         </is>
       </c>
       <c r="E41">
-        <v>-0.291</v>
+        <v>-0.496</v>
       </c>
       <c r="F41">
-        <v>0.127</v>
+        <v>0.113</v>
       </c>
       <c r="G41">
-        <v>-0.553</v>
+        <v>-0.722</v>
       </c>
       <c r="H41">
-        <v>-0.051</v>
+        <v>-0.28</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2024,16 +2024,16 @@
         </is>
       </c>
       <c r="E42">
-        <v>-0.386</v>
+        <v>-0.392</v>
       </c>
       <c r="F42">
-        <v>0.138</v>
+        <v>0.139</v>
       </c>
       <c r="G42">
-        <v>-0.66</v>
+        <v>-0.664</v>
       </c>
       <c r="H42">
-        <v>-0.11</v>
+        <v>-0.119</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2064,16 +2064,16 @@
         </is>
       </c>
       <c r="E43">
-        <v>-0.183</v>
+        <v>-0.197</v>
       </c>
       <c r="F43">
-        <v>0.135</v>
+        <v>0.142</v>
       </c>
       <c r="G43">
-        <v>-0.465</v>
+        <v>-0.493</v>
       </c>
       <c r="H43">
-        <v>0.065</v>
+        <v>0.052</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2104,16 +2104,16 @@
         </is>
       </c>
       <c r="E44">
-        <v>-0.165</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F44">
-        <v>0.313</v>
+        <v>0.33</v>
       </c>
       <c r="G44">
-        <v>-0.837</v>
+        <v>-0.709</v>
       </c>
       <c r="H44">
-        <v>0.434</v>
+        <v>0.584</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         </is>
       </c>
       <c r="E45">
-        <v>-1.324</v>
+        <v>-1.239</v>
       </c>
       <c r="F45">
-        <v>0.326</v>
+        <v>0.332</v>
       </c>
       <c r="G45">
-        <v>-1.966</v>
+        <v>-1.905</v>
       </c>
       <c r="H45">
-        <v>-0.695</v>
+        <v>-0.594</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2184,16 +2184,16 @@
         </is>
       </c>
       <c r="E46">
-        <v>-2.182</v>
+        <v>-2.238</v>
       </c>
       <c r="F46">
-        <v>0.356</v>
+        <v>0.402</v>
       </c>
       <c r="G46">
-        <v>-2.996</v>
+        <v>-3.041</v>
       </c>
       <c r="H46">
-        <v>-1.53</v>
+        <v>-1.469</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2224,20 +2224,20 @@
         </is>
       </c>
       <c r="E47">
-        <v>-1.719</v>
+        <v>-1.547</v>
       </c>
       <c r="F47">
-        <v>0.929</v>
+        <v>0.926</v>
       </c>
       <c r="G47">
-        <v>-3.683</v>
+        <v>-3.577</v>
       </c>
       <c r="H47">
-        <v>-0.101</v>
+        <v>0.002</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Negative (-)</t>
+          <t>Overlap 0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -2264,16 +2264,16 @@
         </is>
       </c>
       <c r="E48">
-        <v>-0.522</v>
+        <v>-0.585</v>
       </c>
       <c r="F48">
-        <v>0.579</v>
+        <v>0.574</v>
       </c>
       <c r="G48">
-        <v>-1.975</v>
+        <v>-1.995</v>
       </c>
       <c r="H48">
-        <v>0.313</v>
+        <v>0.237</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         </is>
       </c>
       <c r="E49">
-        <v>-1.346</v>
+        <v>-1.322</v>
       </c>
       <c r="F49">
-        <v>0.289</v>
+        <v>0.307</v>
       </c>
       <c r="G49">
-        <v>-1.92</v>
+        <v>-1.942</v>
       </c>
       <c r="H49">
-        <v>-0.801</v>
+        <v>-0.745</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2344,16 +2344,16 @@
         </is>
       </c>
       <c r="E50">
-        <v>-2.418</v>
+        <v>-2.334</v>
       </c>
       <c r="F50">
-        <v>0.307</v>
+        <v>0.334</v>
       </c>
       <c r="G50">
-        <v>-3.068</v>
+        <v>-2.995</v>
       </c>
       <c r="H50">
-        <v>-1.862</v>
+        <v>-1.675</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2384,20 +2384,20 @@
         </is>
       </c>
       <c r="E51">
-        <v>-1.685</v>
+        <v>-1.622</v>
       </c>
       <c r="F51">
-        <v>1.03</v>
+        <v>0.916</v>
       </c>
       <c r="G51">
-        <v>-3.883</v>
+        <v>-3.586</v>
       </c>
       <c r="H51">
-        <v>0.016</v>
+        <v>-0.091</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Overlap 0</t>
+          <t>Negative (-)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2424,16 +2424,16 @@
         </is>
       </c>
       <c r="E52">
-        <v>-1.181</v>
+        <v>-1.245</v>
       </c>
       <c r="F52">
-        <v>0.35</v>
+        <v>0.312</v>
       </c>
       <c r="G52">
-        <v>-1.863</v>
+        <v>-1.876</v>
       </c>
       <c r="H52">
-        <v>-0.473</v>
+        <v>-0.638</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="E53">
-        <v>-2.373</v>
+        <v>-2.238</v>
       </c>
       <c r="F53">
-        <v>0.349</v>
+        <v>0.331</v>
       </c>
       <c r="G53">
-        <v>-3.088</v>
+        <v>-2.884</v>
       </c>
       <c r="H53">
-        <v>-1.693</v>
+        <v>-1.601</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2504,16 +2504,16 @@
         </is>
       </c>
       <c r="E54">
-        <v>-1.694</v>
+        <v>-1.649</v>
       </c>
       <c r="F54">
-        <v>0.9330000000000001</v>
+        <v>0.958</v>
       </c>
       <c r="G54">
-        <v>-3.739</v>
+        <v>-3.761</v>
       </c>
       <c r="H54">
-        <v>-0.152</v>
+        <v>-0.079</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2544,16 +2544,16 @@
         </is>
       </c>
       <c r="E55">
-        <v>-0.5639999999999999</v>
+        <v>-0.574</v>
       </c>
       <c r="F55">
-        <v>0.549</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="G55">
-        <v>-1.961</v>
+        <v>-1.974</v>
       </c>
       <c r="H55">
-        <v>0.204</v>
+        <v>0.232</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2584,20 +2584,20 @@
         </is>
       </c>
       <c r="E56">
-        <v>0.481</v>
+        <v>0.477</v>
       </c>
       <c r="F56">
-        <v>0.217</v>
+        <v>0.249</v>
       </c>
       <c r="G56">
-        <v>0.042</v>
+        <v>-0.02</v>
       </c>
       <c r="H56">
-        <v>0.902</v>
+        <v>0.959</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Positive (+)</t>
+          <t>Overlap 0</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -2624,16 +2624,16 @@
         </is>
       </c>
       <c r="E57">
-        <v>0.444</v>
+        <v>0.461</v>
       </c>
       <c r="F57">
-        <v>0.247</v>
+        <v>0.25</v>
       </c>
       <c r="G57">
-        <v>-0.047</v>
+        <v>-0.035</v>
       </c>
       <c r="H57">
-        <v>0.909</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2664,16 +2664,16 @@
         </is>
       </c>
       <c r="E58">
-        <v>-0.678</v>
+        <v>-0.792</v>
       </c>
       <c r="F58">
-        <v>1.026</v>
+        <v>0.956</v>
       </c>
       <c r="G58">
-        <v>-3.218</v>
+        <v>-3.065</v>
       </c>
       <c r="H58">
-        <v>0.552</v>
+        <v>0.448</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>

--- a/Results/tables/Ecological_Covariate_Effects_Synthesis.xlsx
+++ b/Results/tables/Ecological_Covariate_Effects_Synthesis.xlsx
@@ -442,7 +442,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2242,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Active in Model (w = 1.0)</t>
+          <t>In model (fixed covariate set; not estimated)</t>
         </is>
       </c>
     </row>
